--- a/sources/table_normalization/xlsx/economy-table132.xlsx
+++ b/sources/table_normalization/xlsx/economy-table132.xlsx
@@ -168,8 +168,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="#0.000"/>
-    <numFmt numFmtId="169" formatCode="#0.0"/>
+    <numFmt numFmtId="164" formatCode="#0.000"/>
+    <numFmt numFmtId="165" formatCode="#0.0"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -233,10 +233,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -248,22 +248,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -549,27 +549,27 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
@@ -585,23 +585,23 @@
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" s="1" customFormat="1" ht="29">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15" t="s">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="15"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:7" ht="31.5" customHeight="1">
       <c r="A5" s="4"/>
@@ -1333,7 +1333,7 @@
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="14" t="s">
         <v>42</v>
       </c>
       <c r="C41" s="4"/>
